--- a/REAP_2026_FAQ.xlsx
+++ b/REAP_2026_FAQ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BCCC194-F2D9-4D7B-B632-49B404D1D6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5732A0F-A01F-4818-BD18-221964FE2FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,9 +310,6 @@
     <t>I am an out-of-Rajasthan candidate. Am I eligible for Government Aided seats in Rajasthan institutions?</t>
   </si>
   <si>
-    <t xml:space="preserve"> Rajasthan </t>
-  </si>
-  <si>
     <t>No, you cannot take admission on Government Aided Seats.</t>
   </si>
   <si>
@@ -332,6 +329,9 @@
   </si>
   <si>
     <t>For the REAP-2026 session, there are a total of 27,627 seats spread across 73 participating institutions. This includes 7,536 seats in Government colleges and 20,091 in Private colleges.</t>
+  </si>
+  <si>
+    <t>government aided, out of state, other state, eligible, gujarat, haryana, up</t>
   </si>
 </sst>
 </file>
@@ -698,7 +698,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="120.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="63.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="255.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1186,10 +1186,10 @@
         <v>95</v>
       </c>
       <c r="C35" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" t="s">
         <v>96</v>
-      </c>
-      <c r="D35" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1197,13 +1197,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>97</v>
+      </c>
+      <c r="C36" t="s">
         <v>98</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>99</v>
-      </c>
-      <c r="D36" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,13 +1211,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
         <v>101</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>102</v>
-      </c>
-      <c r="D37" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
